--- a/source-data/Enerium_Ритуалы.xlsx
+++ b/source-data/Enerium_Ритуалы.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вкладки'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Имена ритуалов'!$A$1:$C$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Пассивки Памяти'!$A$1:$D$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Правила'!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Правила'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Тексты'!$A$1:$B$7</definedName>
   </definedNames>
 </workbook>
@@ -165,7 +165,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -177,7 +177,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8d0ab64bd187cd14 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">741dbcb440e4ad83 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -250,7 +250,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 строк.</t>
+          <t xml:space="preserve">15 строк.</t>
         </is>
       </c>
     </row>
@@ -292,8 +292,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -1551,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1732,8 +1732,20 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ladder</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mode":"ritual","weekH":168}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B16"/>
 </worksheet>
 </file>
 
